--- a/templates/HS-AUDIT-TEMPLATE.xlsx
+++ b/templates/HS-AUDIT-TEMPLATE.xlsx
@@ -753,7 +753,7 @@
       <c r="G8" s="11" t="n"/>
       <c r="H8" s="11" t="n"/>
       <c r="I8" s="12">
-        <f>IF(AND(N(G8)&gt;0,H8&lt;&gt;""),H8/G8,"N/A")</f>
+        <f>IF(AND(N(G8)&gt;0,H8&lt;&gt;""),ROUND(H8/G8,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -781,7 +781,7 @@
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>IFERROR(AVERAGE(I10:I21),"N/A")</f>
+        <f>IFERROR(ROUND(AVERAGE(I10:I21),4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -799,7 +799,7 @@
       <c r="G10" s="11" t="n"/>
       <c r="H10" s="11" t="n"/>
       <c r="I10" s="12">
-        <f>IF(AND(N(G10)&gt;0,H10&lt;&gt;""),H10/G10,"N/A")</f>
+        <f>IF(AND(N(G10)&gt;0,H10&lt;&gt;""),ROUND(H10/G10,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -817,7 +817,7 @@
       <c r="G11" s="11" t="n"/>
       <c r="H11" s="11" t="n"/>
       <c r="I11" s="12">
-        <f>IF(AND(N(G11)&gt;0,H11&lt;&gt;""),H11/G11,"N/A")</f>
+        <f>IF(AND(N(G11)&gt;0,H11&lt;&gt;""),ROUND(H11/G11,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -835,7 +835,7 @@
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="12">
-        <f>IF(AND(N(G12)&gt;0,H12&lt;&gt;""),H12/G12,"N/A")</f>
+        <f>IF(AND(N(G12)&gt;0,H12&lt;&gt;""),ROUND(H12/G12,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -853,7 +853,7 @@
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n"/>
       <c r="I13" s="12">
-        <f>IF(AND(N(G13)&gt;0,H13&lt;&gt;""),H13/G13,"N/A")</f>
+        <f>IF(AND(N(G13)&gt;0,H13&lt;&gt;""),ROUND(H13/G13,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -871,7 +871,7 @@
       <c r="G14" s="11" t="n"/>
       <c r="H14" s="11" t="n"/>
       <c r="I14" s="12">
-        <f>IF(AND(N(G14)&gt;0,H14&lt;&gt;""),H14/G14,"N/A")</f>
+        <f>IF(AND(N(G14)&gt;0,H14&lt;&gt;""),ROUND(H14/G14,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -889,7 +889,7 @@
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="12">
-        <f>IF(AND(N(G15)&gt;0,H15&lt;&gt;""),H15/G15,"N/A")</f>
+        <f>IF(AND(N(G15)&gt;0,H15&lt;&gt;""),ROUND(H15/G15,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -907,7 +907,7 @@
       <c r="G16" s="11" t="n"/>
       <c r="H16" s="11" t="n"/>
       <c r="I16" s="12">
-        <f>IF(AND(N(G16)&gt;0,H16&lt;&gt;""),H16/G16,"N/A")</f>
+        <f>IF(AND(N(G16)&gt;0,H16&lt;&gt;""),ROUND(H16/G16,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -925,7 +925,7 @@
       <c r="G17" s="11" t="n"/>
       <c r="H17" s="11" t="n"/>
       <c r="I17" s="12">
-        <f>IF(AND(N(G17)&gt;0,H17&lt;&gt;""),H17/G17,"N/A")</f>
+        <f>IF(AND(N(G17)&gt;0,H17&lt;&gt;""),ROUND(H17/G17,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -943,7 +943,7 @@
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="n"/>
       <c r="I18" s="12">
-        <f>IF(AND(N(G18)&gt;0,H18&lt;&gt;""),H18/G18,"N/A")</f>
+        <f>IF(AND(N(G18)&gt;0,H18&lt;&gt;""),ROUND(H18/G18,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -961,7 +961,7 @@
       <c r="G19" s="11" t="n"/>
       <c r="H19" s="11" t="n"/>
       <c r="I19" s="12">
-        <f>IF(AND(N(G19)&gt;0,H19&lt;&gt;""),H19/G19,"N/A")</f>
+        <f>IF(AND(N(G19)&gt;0,H19&lt;&gt;""),ROUND(H19/G19,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -979,7 +979,7 @@
       <c r="G20" s="11" t="n"/>
       <c r="H20" s="11" t="n"/>
       <c r="I20" s="12">
-        <f>IF(AND(N(G20)&gt;0,H20&lt;&gt;""),H20/G20,"N/A")</f>
+        <f>IF(AND(N(G20)&gt;0,H20&lt;&gt;""),ROUND(H20/G20,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -997,7 +997,7 @@
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
       <c r="I21" s="12">
-        <f>IF(AND(N(G21)&gt;0,H21&lt;&gt;""),H21/G21,"N/A")</f>
+        <f>IF(AND(N(G21)&gt;0,H21&lt;&gt;""),ROUND(H21/G21,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>IFERROR(AVERAGE(I23:I24),"N/A")</f>
+        <f>IFERROR(ROUND(AVERAGE(I23:I24),4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       <c r="G23" s="11" t="n"/>
       <c r="H23" s="11" t="n"/>
       <c r="I23" s="12">
-        <f>IF(AND(N(G23)&gt;0,H23&lt;&gt;""),H23/G23,"N/A")</f>
+        <f>IF(AND(N(G23)&gt;0,H23&lt;&gt;""),ROUND(H23/G23,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       <c r="G24" s="11" t="n"/>
       <c r="H24" s="11" t="n"/>
       <c r="I24" s="12">
-        <f>IF(AND(N(G24)&gt;0,H24&lt;&gt;""),H24/G24,"N/A")</f>
+        <f>IF(AND(N(G24)&gt;0,H24&lt;&gt;""),ROUND(H24/G24,4),"N/A")</f>
         <v/>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="2" t="n"/>
       <c r="G25" s="18">
-        <f>IFERROR(AVERAGE(I8,I9,I22),"N/A")</f>
+        <f>IFERROR(ROUND(AVERAGE(I8,I9,I22),4),"N/A")</f>
         <v/>
       </c>
       <c r="H25" s="19" t="inlineStr">
@@ -1565,7 +1565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1703,34 +1703,46 @@
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>For more than one contractor:</t>
+          <t>NAME THE SHEET LIKE THIS:</t>
         </is>
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>copy A1:I31 on the AUDIT TEMPLATE sheet and paste at K1, then U1, then AE1 — ten columns apart. The formulas are relative and follow. The importer expects that spacing.</t>
+          <t>"Q2 2026 SUBREGION1" — quarter, year and sub-region. The importer and the verifier both find a quarter's sheet by that pattern, and will skip a sheet called anything else. One sheet per quarter per sub-region.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>WHAT NOT TO DO:</t>
+          <t>For more than one contractor:</t>
         </is>
       </c>
       <c r="B23" s="32" t="inlineStr">
         <is>
-          <t>do not insert or delete rows inside the block, and do not move the points into different columns. The importer reads fixed rows and columns. Run scripts/verify-against-sheet.py against the finished workbook before trusting an import — it reads by label instead, so it catches a shifted row.</t>
+          <t>copy A1:I31 on the AUDIT TEMPLATE sheet and paste at K1, then U1, then AE1 — ten columns apart. The formulas are relative and follow. The importer expects that spacing.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
         <is>
+          <t>WHAT NOT TO DO:</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>do not insert or delete rows inside the block, and do not move the points into different columns. The importer reads fixed rows and columns. Run scripts/verify-against-sheet.py against the finished workbook before trusting an import — it reads by label instead, so it catches a shifted row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="inlineStr">
+        <is>
           <t>WHY THIS TEMPLATE EXISTS:</t>
         </is>
       </c>
-      <c r="B25" s="32" t="inlineStr">
+      <c r="B27" s="32" t="inlineStr">
         <is>
           <t>the Q4 2025 and Q1 2026 workbooks contained no formulas at all. Every percentage and total was typed, 32 of them had drifted from the points beside them, and no rule explained the stated total in 11 of 20 audits.</t>
         </is>
